--- a/1 lesson/temp/Подсети.xlsx
+++ b/1 lesson/temp/Подсети.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="224">
   <si>
     <t>Параметр</t>
   </si>
@@ -41,9 +41,6 @@
     <t>Адресов в подсети</t>
   </si>
   <si>
-    <t>Всего подсетей</t>
-  </si>
-  <si>
     <t>Занятый диапазон</t>
   </si>
   <si>
@@ -521,9 +518,6 @@
     <t>8 (6 хоста + сеть + broadcast)</t>
   </si>
   <si>
-    <t>10.0.0.0 — 10.0.1.143</t>
-  </si>
-  <si>
     <t>Общая сеть</t>
   </si>
   <si>
@@ -611,9 +605,6 @@
     <t>98 R24 e0/0</t>
   </si>
   <si>
-    <t>ip address 10.0.0.74 255.255.255.248</t>
-  </si>
-  <si>
     <t>Окночание ip, хост, порт</t>
   </si>
   <si>
@@ -702,6 +693,9 @@
   </si>
   <si>
     <t>218 R16 e0/2</t>
+  </si>
+  <si>
+    <t>10.0.0.0 — 10.0.0.222</t>
   </si>
 </sst>
 </file>
@@ -780,17 +774,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1091,249 +1085,240 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="3"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>170</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="M2" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>172</v>
+      <c r="E3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="M3" s="4"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>174</v>
+      <c r="E4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="M4" s="4"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>176</v>
+      <c r="E5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="M5" s="4"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>178</v>
+      <c r="E6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4">
-        <v>50</v>
-      </c>
-      <c r="M6" s="4"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>180</v>
+      <c r="E7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="M7" s="4"/>
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>182</v>
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1341,52 +1326,50 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>184</v>
+      <c r="E9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>186</v>
+      <c r="E10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1394,22 +1377,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>188</v>
+      <c r="E11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1417,22 +1400,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>190</v>
+      <c r="E12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1440,22 +1423,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>192</v>
+      <c r="E13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1463,22 +1446,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>194</v>
+      <c r="E14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1486,22 +1469,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>198</v>
+      <c r="E15" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1509,22 +1492,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>200</v>
+      <c r="E16" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1532,22 +1515,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>202</v>
+      <c r="E17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1555,22 +1538,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>204</v>
+      <c r="E18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1578,22 +1561,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>206</v>
+      <c r="E19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1601,22 +1584,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>208</v>
+      <c r="E20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1624,22 +1607,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>210</v>
+      <c r="E21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1647,22 +1630,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>213</v>
+      <c r="E22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1670,22 +1653,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>214</v>
+      <c r="E23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1693,20 +1676,20 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F24" s="6"/>
+      <c r="E24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1714,22 +1697,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>217</v>
+      <c r="E25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1737,22 +1720,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>219</v>
+      <c r="E26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1760,22 +1743,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1783,22 +1766,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1806,22 +1789,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1829,18 +1812,18 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1848,18 +1831,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1867,18 +1850,18 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1886,18 +1869,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1905,18 +1888,18 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1924,18 +1907,18 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1943,18 +1926,18 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1962,18 +1945,18 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1981,18 +1964,18 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2000,18 +1983,18 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2019,18 +2002,18 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2038,18 +2021,18 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2057,18 +2040,18 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2076,18 +2059,18 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2095,18 +2078,18 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2114,18 +2097,18 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2133,18 +2116,18 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2152,18 +2135,18 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2171,18 +2154,18 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2190,18 +2173,18 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2209,18 +2192,18 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2228,35 +2211,33 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="13">
     <mergeCell ref="I9:M9"/>
-    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L6:M6"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="L6:M6"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:M2"/>
   </mergeCells>

--- a/1 lesson/temp/Подсети.xlsx
+++ b/1 lesson/temp/Подсети.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="234">
   <si>
     <t>Параметр</t>
   </si>
@@ -527,18 +527,6 @@
     <t xml:space="preserve">10.0.0.1 – 10.0.0.6 </t>
   </si>
   <si>
-    <t>1 R12 e0/0</t>
-  </si>
-  <si>
-    <t>2 R13 e0/0</t>
-  </si>
-  <si>
-    <t>9 R12 e0/1</t>
-  </si>
-  <si>
-    <t>10 R13 e0/1</t>
-  </si>
-  <si>
     <t xml:space="preserve">17 R12 e0/2  </t>
   </si>
   <si>
@@ -662,9 +650,6 @@
     <t>170 R18 e0/3</t>
   </si>
   <si>
-    <t>177 R28 e0/2</t>
-  </si>
-  <si>
     <t>185 R18 e0/1</t>
   </si>
   <si>
@@ -683,26 +668,71 @@
     <t>202 R32 e0/0</t>
   </si>
   <si>
-    <t>209 R17 e0/0</t>
-  </si>
-  <si>
-    <t>210 R16 e0/0</t>
-  </si>
-  <si>
-    <t>217 R17 e0/2</t>
-  </si>
-  <si>
-    <t>218 R16 e0/2</t>
-  </si>
-  <si>
-    <t>10.0.0.0 — 10.0.0.222</t>
+    <t>10.0.0.0 — 10.0.0.255</t>
+  </si>
+  <si>
+    <t>native vlan 1000</t>
+  </si>
+  <si>
+    <t>233 vpc7 234 sw2             235 sw5 236 R12 e0/1.3     237 R13 e0/0.3</t>
+  </si>
+  <si>
+    <t>209 vpc8        210 sw9             211 R17 e0/0.4 212 R16 e0/2.4</t>
+  </si>
+  <si>
+    <t>217 vpc       218 sw10              219 R16 e0/0.9   220 R17 e0/2.9</t>
+  </si>
+  <si>
+    <t>225 vpc1 226 sw3                 227 sw4 228 R12 e0/0.2    229 R13 e0/1.2</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Vlan</t>
+  </si>
+  <si>
+    <t>vpc1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> vlan 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vpc7 </t>
+  </si>
+  <si>
+    <t>vlan 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vpc8 </t>
+  </si>
+  <si>
+    <t>vlan 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vpc </t>
+  </si>
+  <si>
+    <t>vlan 9</t>
+  </si>
+  <si>
+    <t>vlan 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vpc30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">vpc31  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 vpc30     2 vpc31                  3 sw29  4 R28 e0/2.10 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -739,8 +769,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -750,6 +787,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF18181A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE32D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB759D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,7 +845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
@@ -777,14 +856,34 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -794,6 +893,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFAB759D"/>
+      <color rgb="FFB56BB0"/>
       <color rgb="FFEE32D3"/>
     </mruColors>
   </colors>
@@ -1080,6 +1181,9 @@
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="41.5703125" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="16" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1097,25 +1201,25 @@
         <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5" t="s">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1128,24 +1232,22 @@
       <c r="D2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>168</v>
-      </c>
+      <c r="E2" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="M2" s="5"/>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1160,24 +1262,20 @@
       <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="5" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="M3" s="6"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1192,24 +1290,24 @@
       <c r="D4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>172</v>
+      <c r="E4" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="5" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1224,24 +1322,24 @@
       <c r="D5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>174</v>
+      <c r="E5" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="5" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1256,24 +1354,24 @@
       <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>176</v>
+      <c r="E6" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="6"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1288,17 +1386,17 @@
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>178</v>
+      <c r="E7" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>174</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1311,14 +1409,20 @@
       <c r="D8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>180</v>
+      <c r="E8" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1334,20 +1438,23 @@
       <c r="D9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>182</v>
+      <c r="E9" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="I9" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1362,14 +1469,20 @@
       <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>184</v>
+      <c r="E10" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1385,15 +1498,22 @@
       <c r="D11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>186</v>
+      <c r="E11" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1408,14 +1528,20 @@
       <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>188</v>
+      <c r="E12" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1431,14 +1557,20 @@
       <c r="D13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>190</v>
+      <c r="E13" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>186</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1454,17 +1586,23 @@
       <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>192</v>
+      <c r="E14" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I14" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1477,14 +1615,18 @@
       <c r="D15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>195</v>
+      <c r="E15" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1500,11 +1642,11 @@
       <c r="D16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>197</v>
+      <c r="E16" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>193</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>22</v>
@@ -1523,11 +1665,11 @@
       <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>199</v>
+      <c r="E17" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>23</v>
@@ -1546,11 +1688,11 @@
       <c r="D18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>201</v>
+      <c r="E18" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>24</v>
@@ -1569,11 +1711,11 @@
       <c r="D19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>203</v>
+      <c r="E19" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>25</v>
@@ -1592,11 +1734,11 @@
       <c r="D20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>205</v>
+      <c r="E20" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>26</v>
@@ -1615,11 +1757,11 @@
       <c r="D21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>207</v>
+      <c r="E21" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>203</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>27</v>
@@ -1638,11 +1780,11 @@
       <c r="D22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>210</v>
+      <c r="E22" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>206</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>28</v>
@@ -1661,11 +1803,11 @@
       <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>211</v>
+      <c r="E23" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>29</v>
@@ -1684,9 +1826,7 @@
       <c r="D24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="1" t="s">
         <v>30</v>
@@ -1705,11 +1845,11 @@
       <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>214</v>
+      <c r="E25" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>31</v>
@@ -1728,11 +1868,11 @@
       <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>216</v>
+      <c r="E26" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
@@ -1751,17 +1891,17 @@
       <c r="D27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>218</v>
+      <c r="E27" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>213</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1774,17 +1914,15 @@
       <c r="D28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="E28" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1797,17 +1935,15 @@
       <c r="D29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="E29" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1820,13 +1956,15 @@
       <c r="D30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="E30" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1839,8 +1977,10 @@
       <c r="D31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="E31" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="1" t="s">
         <v>100</v>
       </c>
@@ -2226,8 +2366,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="I9:M9"/>
+  <mergeCells count="12">
     <mergeCell ref="L6:M6"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I3:K3"/>

--- a/1 lesson/temp/Подсети.xlsx
+++ b/1 lesson/temp/Подсети.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="238">
   <si>
     <t>Параметр</t>
   </si>
@@ -726,6 +726,18 @@
   </si>
   <si>
     <t xml:space="preserve">1 vpc30     2 vpc31                  3 sw29  4 R28 e0/2.10 </t>
+  </si>
+  <si>
+    <t>241  r12 e1/0</t>
+  </si>
+  <si>
+    <t>242  r13 e1/0</t>
+  </si>
+  <si>
+    <t>249 R14 e1/0</t>
+  </si>
+  <si>
+    <t>250 R15 e1/0</t>
   </si>
 </sst>
 </file>
@@ -856,12 +868,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -884,6 +890,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1209,15 +1221,15 @@
       <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="4"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1232,22 +1244,22 @@
       <c r="D2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="12" t="s">
         <v>233</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="M2" s="4"/>
+      <c r="M2" s="13"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1267,15 +1279,15 @@
       <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="4" t="s">
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1290,24 +1302,24 @@
       <c r="D4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="9" t="s">
         <v>168</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="M4" s="5"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1322,24 +1334,24 @@
       <c r="D5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
         <v>170</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="4" t="s">
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="M5" s="5"/>
+      <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1354,24 +1366,24 @@
       <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="9" t="s">
         <v>172</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4" t="s">
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="M6" s="5"/>
+      <c r="M6" s="14"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1386,10 +1398,10 @@
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>174</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1409,10 +1421,10 @@
       <c r="D8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
         <v>176</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1438,10 +1450,10 @@
       <c r="D9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>178</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1453,8 +1465,8 @@
       <c r="J9" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1469,10 +1481,10 @@
       <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>180</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1498,10 +1510,10 @@
       <c r="D11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1513,7 +1525,7 @@
       <c r="J11" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="K11" s="7"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1528,10 +1540,10 @@
       <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="11" t="s">
         <v>184</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1557,10 +1569,10 @@
       <c r="D13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>186</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1586,10 +1598,10 @@
       <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1615,10 +1627,10 @@
       <c r="D15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>191</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1642,10 +1654,10 @@
       <c r="D16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>193</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1665,10 +1677,10 @@
       <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>195</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1688,10 +1700,10 @@
       <c r="D18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>197</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1711,10 +1723,10 @@
       <c r="D19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>199</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1734,10 +1746,10 @@
       <c r="D20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>201</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1757,10 +1769,10 @@
       <c r="D21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="12" t="s">
         <v>203</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -1780,10 +1792,10 @@
       <c r="D22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="12" t="s">
         <v>206</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -1803,10 +1815,10 @@
       <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="7" t="s">
         <v>207</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1845,10 +1857,10 @@
       <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="7" t="s">
         <v>209</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -1868,10 +1880,10 @@
       <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="7" t="s">
         <v>211</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -1891,10 +1903,10 @@
       <c r="D27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>213</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -1914,7 +1926,7 @@
       <c r="D28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>217</v>
       </c>
       <c r="F28" s="3"/>
@@ -1935,7 +1947,7 @@
       <c r="D29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="7" t="s">
         <v>218</v>
       </c>
       <c r="F29" s="3"/>
@@ -1956,7 +1968,7 @@
       <c r="D30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="9" t="s">
         <v>219</v>
       </c>
       <c r="F30" s="3"/>
@@ -1977,7 +1989,7 @@
       <c r="D31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="9" t="s">
         <v>216</v>
       </c>
       <c r="F31" s="3"/>
@@ -1998,8 +2010,12 @@
       <c r="D32" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="E32" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="G32" s="1" t="s">
         <v>103</v>
       </c>
@@ -2017,8 +2033,12 @@
       <c r="D33" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="E33" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="G33" s="1" t="s">
         <v>106</v>
       </c>
